--- a/____EvoM1_TraitTable/corticospinal_terminations.xlsx
+++ b/____EvoM1_TraitTable/corticospinal_terminations.xlsx
@@ -762,13 +762,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F16DB5A4-F7E9-4A6D-BEA3-3168FA65B911}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97C6C701-F74A-4381-B611-48809906DB3D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FC62A3E-AE63-4959-915B-7452D32CCBFA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{687789E9-808D-4198-879B-9AE870F11762}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B12AF93D-DCAC-4280-87B4-412D48C4E21D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDF0D1A1-2CB0-46DD-A4C9-9C4E94509BBB}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinal_terminations.xlsx
+++ b/____EvoM1_TraitTable/corticospinal_terminations.xlsx
@@ -762,13 +762,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97C6C701-F74A-4381-B611-48809906DB3D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79A90C73-B4F7-4F19-A33E-F3F8550CA469}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{687789E9-808D-4198-879B-9AE870F11762}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F246B1A-FB9F-4992-8338-FABE2F572532}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDF0D1A1-2CB0-46DD-A4C9-9C4E94509BBB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5920A969-6548-4291-B70B-87E984B5B131}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinal_terminations.xlsx
+++ b/____EvoM1_TraitTable/corticospinal_terminations.xlsx
@@ -762,13 +762,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79A90C73-B4F7-4F19-A33E-F3F8550CA469}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D76FF8D-FC1A-47B0-AA80-7F7083740B56}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F246B1A-FB9F-4992-8338-FABE2F572532}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5C3575E-91D6-41C7-8944-AA5336FA267B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5920A969-6548-4291-B70B-87E984B5B131}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E2F554F-56CF-4914-B357-AE4303114229}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinal_terminations.xlsx
+++ b/____EvoM1_TraitTable/corticospinal_terminations.xlsx
@@ -762,13 +762,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D76FF8D-FC1A-47B0-AA80-7F7083740B56}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37EBB84E-0470-44E8-A201-6CB609461873}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5C3575E-91D6-41C7-8944-AA5336FA267B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB2C135E-5AB6-41C6-BC7C-1B93A1824038}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E2F554F-56CF-4914-B357-AE4303114229}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52EF25B3-BCE6-4A29-A049-4D0DD950088B}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinal_terminations.xlsx
+++ b/____EvoM1_TraitTable/corticospinal_terminations.xlsx
@@ -11,6 +11,65 @@
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
+  <si>
+    <t>species_sci</t>
+  </si>
+  <si>
+    <t>Species</t>
+  </si>
+  <si>
+    <t>Species_printed</t>
+  </si>
+  <si>
+    <t>CST_termination_grade</t>
+  </si>
+  <si>
+    <t>CM_monosynaptic</t>
+  </si>
+  <si>
+    <t>CM_connection_inference</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>DOI</t>
+  </si>
+  <si>
+    <t>Source_location</t>
+  </si>
+  <si>
+    <t>Sapajus apella</t>
+  </si>
+  <si>
+    <t>Cebus apella</t>
+  </si>
+  <si>
+    <t>likely</t>
+  </si>
+  <si>
+    <t>Bortoff &amp; Strick 1993</t>
+  </si>
+  <si>
+    <t>10.1523/JNEUROSCI.13-12-05105.1993</t>
+  </si>
+  <si>
+    <t>Abstract; Results pp. 5108-5111; Figures 3, 5-11</t>
+  </si>
+  <si>
+    <t>Saimiri sciureus</t>
+  </si>
+  <si>
+    <t>against</t>
+  </si>
+  <si>
+    <t>Abstract; Results pp. 5109-5111; Figures 4, 6, 10-11</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -354,131 +413,85 @@
   <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>species_sci</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Species</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Species_printed</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>CST_termination_grade</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>CM_monosynaptic</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>CM_connection_inference</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>DOI</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Source_location</t>
-        </is>
+    <row r="1" spans="1:9" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Sapajus apella</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Sapajus apella</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Cebus apella</t>
-        </is>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
       </c>
       <c r="D2">
         <v>2</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>likely</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Bortoff &amp; Strick 1993</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>10.1523/JNEUROSCI.13-12-05105.1993</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Abstract; Results pp. 5108-5111; Figures 3, 5-11</t>
-        </is>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Saimiri sciureus</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Saimiri sciureus</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Saimiri sciureus</t>
-        </is>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>against</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Bortoff &amp; Strick 1993</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>10.1523/JNEUROSCI.13-12-05105.1993</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Abstract; Results pp. 5109-5111; Figures 4, 6, 10-11</t>
-        </is>
+      <c r="F3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -762,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37EBB84E-0470-44E8-A201-6CB609461873}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB34C729-97B6-4D63-99C7-9F9A733E0E0F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB2C135E-5AB6-41C6-BC7C-1B93A1824038}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{840F5A39-AFFA-4448-AED6-F48B32573D7C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52EF25B3-BCE6-4A29-A049-4D0DD950088B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2741DE63-7597-445A-BE6D-8E06813AF674}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinal_terminations.xlsx
+++ b/____EvoM1_TraitTable/corticospinal_terminations.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB34C729-97B6-4D63-99C7-9F9A733E0E0F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FAA04B28-0139-435C-9978-59EB03B4F6C9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{840F5A39-AFFA-4448-AED6-F48B32573D7C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE907A24-D9F4-4373-8D0C-838F11C7F8AB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2741DE63-7597-445A-BE6D-8E06813AF674}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F31C2EA8-C595-4C90-93AD-6A624E0C59F1}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinal_terminations.xlsx
+++ b/____EvoM1_TraitTable/corticospinal_terminations.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FAA04B28-0139-435C-9978-59EB03B4F6C9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F73ED5BB-6FC6-4788-A71D-256E8662D7CA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE907A24-D9F4-4373-8D0C-838F11C7F8AB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDE57BBF-D4AE-4D04-90EA-7F0D91BEA748}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F31C2EA8-C595-4C90-93AD-6A624E0C59F1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7255118-B28B-489B-9B72-CACE1FB6197C}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinal_terminations.xlsx
+++ b/____EvoM1_TraitTable/corticospinal_terminations.xlsx
@@ -497,291 +497,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F73ED5BB-6FC6-4788-A71D-256E8662D7CA}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDE57BBF-D4AE-4D04-90EA-7F0D91BEA748}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7255118-B28B-489B-9B72-CACE1FB6197C}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinal_terminations.xlsx
+++ b/____EvoM1_TraitTable/corticospinal_terminations.xlsx
@@ -497,4 +497,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE961F2E-4B6F-4F5B-B2CB-DF02A2DB5584}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19F209D7-57E1-400C-A1A4-1F95DB522495}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A2FA713-EA34-4741-81A0-651D464A8EFA}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinal_terminations.xlsx
+++ b/____EvoM1_TraitTable/corticospinal_terminations.xlsx
@@ -497,291 +497,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE961F2E-4B6F-4F5B-B2CB-DF02A2DB5584}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19F209D7-57E1-400C-A1A4-1F95DB522495}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A2FA713-EA34-4741-81A0-651D464A8EFA}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinal_terminations.xlsx
+++ b/____EvoM1_TraitTable/corticospinal_terminations.xlsx
@@ -497,4 +497,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{010A2465-C227-4827-B5C9-EC553AD48D91}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C805A80A-296C-4AA5-9A2A-55C5BAB6208A}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCA4DF39-AB00-42D2-91AF-187A8CF95F70}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinal_terminations.xlsx
+++ b/____EvoM1_TraitTable/corticospinal_terminations.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{010A2465-C227-4827-B5C9-EC553AD48D91}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F7E94F4-D4A5-4716-AFB0-E2FD3E7A984B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C805A80A-296C-4AA5-9A2A-55C5BAB6208A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12282A34-61F2-457F-8A08-CBF2758E6310}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCA4DF39-AB00-42D2-91AF-187A8CF95F70}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D06DEF07-A95D-49BD-BD6E-B369AF7CA162}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinal_terminations.xlsx
+++ b/____EvoM1_TraitTable/corticospinal_terminations.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F7E94F4-D4A5-4716-AFB0-E2FD3E7A984B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7E1C18-85CD-4C58-A6A1-857D4F254884}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12282A34-61F2-457F-8A08-CBF2758E6310}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{678E08DE-575F-4176-8D1C-A7CB01A553A2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D06DEF07-A95D-49BD-BD6E-B369AF7CA162}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB450BB6-6293-4036-B6F5-A22151C3BA7C}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinal_terminations.xlsx
+++ b/____EvoM1_TraitTable/corticospinal_terminations.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7E1C18-85CD-4C58-A6A1-857D4F254884}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16F1BD63-5165-485E-9627-239E7CAC9CC4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{678E08DE-575F-4176-8D1C-A7CB01A553A2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB353EEA-BEC9-4D60-86FB-E14EA0A14127}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB450BB6-6293-4036-B6F5-A22151C3BA7C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65DD8FC2-619B-4033-A886-5269206E8344}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinal_terminations.xlsx
+++ b/____EvoM1_TraitTable/corticospinal_terminations.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16F1BD63-5165-485E-9627-239E7CAC9CC4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1ACE675A-1C61-4035-BA39-F22C6688035A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB353EEA-BEC9-4D60-86FB-E14EA0A14127}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00220932-870B-42BE-A52E-ACF57B406C8E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65DD8FC2-619B-4033-A886-5269206E8344}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B6591CE-CDA9-4240-9EFE-3EE9D993BBE6}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinal_terminations.xlsx
+++ b/____EvoM1_TraitTable/corticospinal_terminations.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1ACE675A-1C61-4035-BA39-F22C6688035A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64B9188D-67BA-481B-A167-C4583BB6B2C5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00220932-870B-42BE-A52E-ACF57B406C8E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CDF56B7-B06B-4FA1-AEF9-96558377AC62}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B6591CE-CDA9-4240-9EFE-3EE9D993BBE6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C678FDA2-FFAF-406F-8510-1D3BA70AEB75}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinal_terminations.xlsx
+++ b/____EvoM1_TraitTable/corticospinal_terminations.xlsx
@@ -497,291 +497,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64B9188D-67BA-481B-A167-C4583BB6B2C5}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CDF56B7-B06B-4FA1-AEF9-96558377AC62}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C678FDA2-FFAF-406F-8510-1D3BA70AEB75}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinal_terminations.xlsx
+++ b/____EvoM1_TraitTable/corticospinal_terminations.xlsx
@@ -497,4 +497,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8EE9EA9-DFCB-4AC8-BCC2-F258B3BE1900}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D3B4493-7592-4BAF-9679-92972B10A3B4}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B34BDED-BFFE-4A6E-B79D-F07FF054D859}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinal_terminations.xlsx
+++ b/____EvoM1_TraitTable/corticospinal_terminations.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8EE9EA9-DFCB-4AC8-BCC2-F258B3BE1900}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08798444-3CF8-41E1-945E-8B8D15993C64}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D3B4493-7592-4BAF-9679-92972B10A3B4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{806AC282-0401-4A0A-9B1A-4150520275BA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B34BDED-BFFE-4A6E-B79D-F07FF054D859}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E1A62FD-6060-4186-A509-E1C7514544A8}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinal_terminations.xlsx
+++ b/____EvoM1_TraitTable/corticospinal_terminations.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08798444-3CF8-41E1-945E-8B8D15993C64}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBE30967-3D53-4893-AE60-96C6E0CE9451}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{806AC282-0401-4A0A-9B1A-4150520275BA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6CE9B1E-AC3B-43A9-9B9D-62EF097868EF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E1A62FD-6060-4186-A509-E1C7514544A8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92EF305D-CD4C-4EC5-9CA7-9A2129F9F84A}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinal_terminations.xlsx
+++ b/____EvoM1_TraitTable/corticospinal_terminations.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBE30967-3D53-4893-AE60-96C6E0CE9451}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4103C557-710E-464C-93F5-1D7E6B261394}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6CE9B1E-AC3B-43A9-9B9D-62EF097868EF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E821D2C-4B7C-4797-A02E-EF93CC937692}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92EF305D-CD4C-4EC5-9CA7-9A2129F9F84A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7089116-51BE-4856-87D4-7BB83CDECC5A}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinal_terminations.xlsx
+++ b/____EvoM1_TraitTable/corticospinal_terminations.xlsx
@@ -497,291 +497,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4103C557-710E-464C-93F5-1D7E6B261394}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E821D2C-4B7C-4797-A02E-EF93CC937692}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7089116-51BE-4856-87D4-7BB83CDECC5A}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinal_terminations.xlsx
+++ b/____EvoM1_TraitTable/corticospinal_terminations.xlsx
@@ -497,4 +497,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0ADFD767-9CC0-4CD8-9592-3D49C003C11A}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10D30C85-2DEC-4915-B956-9FB91E1AFA6D}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5477078-B404-4A9F-9AF2-88EE7FC4B21D}"/>
 </file>